--- a/deliverables/function_list_v2/uiss/XD08_UISS_Batch_OrderControlInfoToNSP_ASN.xlsx
+++ b/deliverables/function_list_v2/uiss/XD08_UISS_Batch_OrderControlInfoToNSP_ASN.xlsx
@@ -11982,7 +11982,7 @@
       <c r="D10" s="941" t="n"/>
       <c r="E10" s="948" t="inlineStr">
         <is>
-          <t>customer order lines of G-TOPAS (replicated in DB Surrounding): rows with</t>
+          <t>customer order lines of G-System (replicated in DB Surrounding): rows with</t>
         </is>
       </c>
       <c r="F10" s="941" t="n"/>
@@ -14804,7 +14804,7 @@
       <c r="BN34" s="955" t="n"/>
       <c r="BO34" s="956" t="inlineStr">
         <is>
-          <t>Scheduler, daily after G-TOPAS has provided the data (27:30);</t>
+          <t>Scheduler, daily after G-System has provided the data (27:30);</t>
         </is>
       </c>
       <c r="BP34" s="957" t="n"/>
@@ -48121,7 +48121,7 @@
       <c r="D11" s="941" t="n"/>
       <c r="E11" s="948" t="inlineStr">
         <is>
-          <t>Transaction table - Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-TOPAS I/F layout; physical names follow</t>
+          <t>Transaction table - Order control data, pre-order picking info (I/F H02-53, DVJO950) replicated from DB Surrounding by XD08 / XD12. Structure from the G-System I/F layout; physical names follow</t>
         </is>
       </c>
       <c r="F11" s="941" t="n"/>
